--- a/outputs/report.xlsx
+++ b/outputs/report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tehokone\.spyder-py3\outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0DBAD9B-A9B7-4DFC-A01D-BD412063D176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE0A3A77-ACBB-4C26-9C72-A12D18FAB3BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6960" yWindow="3510" windowWidth="19590" windowHeight="9360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6360" yWindow="1710" windowWidth="19590" windowHeight="9360" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="failed_logins" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="14">
   <si>
     <t>ip</t>
   </si>
@@ -43,6 +43,9 @@
     <t>10.0.0.5</t>
   </si>
   <si>
+    <t>77.91.12.1</t>
+  </si>
+  <si>
     <t>endpoint</t>
   </si>
   <si>
@@ -50,6 +53,12 @@
   </si>
   <si>
     <t>/login</t>
+  </si>
+  <si>
+    <t>/admin</t>
+  </si>
+  <si>
+    <t>/api/login</t>
   </si>
   <si>
     <t>/dashboard</t>
@@ -421,7 +430,6 @@
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -438,7 +446,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -450,6 +458,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -464,7 +475,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -474,7 +485,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -490,7 +501,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -509,6 +520,14 @@
         <v>1</v>
       </c>
     </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -516,28 +535,28 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -545,9 +564,25 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6">
         <v>1</v>
       </c>
     </row>
